--- a/measurements/37/Filled_2D_sections/sagittal/week37_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/37/Filled_2D_sections/sagittal/week37_sagittal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AF27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,97 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +591,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10.15020820939917</v>
+        <v>3869.047619047619</v>
       </c>
       <c r="D2" t="n">
-        <v>19.49944546164536</v>
+        <v>380.703459013076</v>
       </c>
       <c r="E2" t="n">
-        <v>14.44038806892023</v>
+        <v>281.9313861074901</v>
       </c>
       <c r="F2" t="n">
         <v>1.350340819691241</v>
@@ -525,24 +610,54 @@
         <v>0.3354596530008671</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5535442073170732</v>
+        <v>2.583705357142857</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5915586890243902</v>
+        <v>11.54947916666667</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5723450203252033</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>5.621279761904763</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>5.332961309523809</v>
+      </c>
+      <c r="S2" t="n">
+        <v>11.54947916666667</v>
+      </c>
+      <c r="T2" t="n">
+        <v>9.714006696428571</v>
+      </c>
+      <c r="U2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.583705357142857</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.045758928571428</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.282578656462585</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>10.66771267102915</v>
+      <c r="AF2" s="2" t="n">
+        <v>4066.309523809524</v>
       </c>
     </row>
     <row r="3">
@@ -553,43 +668,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10.86317668054729</v>
+        <v>4140.816326530612</v>
       </c>
       <c r="D3" t="n">
-        <v>17.22392197062329</v>
+        <v>336.2765718074072</v>
       </c>
       <c r="E3" t="n">
-        <v>14.41671581384612</v>
+        <v>281.4692135084243</v>
       </c>
       <c r="F3" t="n">
         <v>1.194718838397374</v>
       </c>
       <c r="G3" t="n">
-        <v>0.460153371465647</v>
+        <v>0.4601533714656471</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6160442073170732</v>
+        <v>1.915922619047619</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6160442073170732</v>
+        <v>12.02752976190476</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6160442073170732</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>4.386470734126983</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>12.02752976190476</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7.994791666666666</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6.813616071428571</v>
+      </c>
+      <c r="U3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.915922619047619</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.0625</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.866856812169312</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>18.13082926142506</v>
+      <c r="AF3" s="2" t="n">
+        <v>353.9828570087751</v>
       </c>
     </row>
     <row r="4">
@@ -600,43 +745,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.92920880428317</v>
+        <v>4165.986394557823</v>
       </c>
       <c r="D4" t="n">
-        <v>17.65804366367619</v>
+        <v>344.7522810527257</v>
       </c>
       <c r="E4" t="n">
-        <v>14.38814087030364</v>
+        <v>280.9113217535473</v>
       </c>
       <c r="F4" t="n">
-        <v>1.227263746084211</v>
+        <v>1.227263746084212</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4404670386957113</v>
+        <v>0.4404670386957112</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5171493902439025</v>
+        <v>1.551339285714286</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5881288109756098</v>
+        <v>11.48251488095238</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5526391006097562</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>4.591918498168498</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6.197916666666666</v>
+      </c>
+      <c r="S4" t="n">
+        <v>11.48251488095238</v>
+      </c>
+      <c r="T4" t="n">
+        <v>8.779296875</v>
+      </c>
+      <c r="U4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.551339285714286</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4.523809523809524</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.730861441798942</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>14.15720230311882</v>
+      <c r="AF4" s="2" t="n">
+        <v>276.4025211561294</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +822,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11.05621653777513</v>
+        <v>4214.399092970521</v>
       </c>
       <c r="D5" t="n">
-        <v>17.64028944911026</v>
+        <v>344.4056511492956</v>
       </c>
       <c r="E5" t="n">
-        <v>14.24670207791212</v>
+        <v>278.1498977116176</v>
       </c>
       <c r="F5" t="n">
         <v>1.238201609933257</v>
@@ -666,23 +841,53 @@
         <v>0.4464830600064129</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5143864329268293</v>
+        <v>1.646205357142857</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5740282012195123</v>
+        <v>11.20721726190476</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5442073170731707</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>4.436383928571429</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>11.20721726190476</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10.04278273809524</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5.79985119047619</v>
+      </c>
+      <c r="U5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.646205357142857</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.503348214285714</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.062313988095238</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AF5" s="2" t="n">
         <v>1.281383877412893</v>
       </c>
     </row>
@@ -694,17 +899,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11.15169541939322</v>
+        <v>4250.79365079365</v>
       </c>
       <c r="D6" t="n">
-        <v>17.01349714325696</v>
+        <v>332.1682775588262</v>
       </c>
       <c r="E6" t="n">
-        <v>14.31568810416431</v>
+        <v>279.4967677479698</v>
       </c>
       <c r="F6" t="n">
         <v>1.188451230528547</v>
@@ -713,23 +918,53 @@
         <v>0.4841317645892251</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5571646341463414</v>
+        <v>1.566220238095238</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5571646341463414</v>
+        <v>10.87797619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5571646341463414</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>3.985570790816327</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>10.87797619047619</v>
+      </c>
+      <c r="P6" t="n">
+        <v>9.155505952380953</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.947916666666666</v>
+      </c>
+      <c r="U6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.566220238095238</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.0234375</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.801508387445887</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AF6" s="2" t="n">
         <v>0.4107589504898279</v>
       </c>
     </row>
@@ -741,43 +976,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11.20761451516954</v>
+        <v>4272.108843537415</v>
       </c>
       <c r="D7" t="n">
-        <v>16.48528118249847</v>
+        <v>321.8554897535415</v>
       </c>
       <c r="E7" t="n">
-        <v>14.30731872232949</v>
+        <v>279.3333655311948</v>
       </c>
       <c r="F7" t="n">
         <v>1.152227157473596</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5182392841836264</v>
+        <v>0.5182392841836267</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5740282012195123</v>
+        <v>2.209821428571428</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5740282012195123</v>
+        <v>11.20721726190476</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5740282012195123</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>4.128534226190476</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>11.20721726190476</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5.17485119047619</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.886532738095238</v>
+      </c>
+      <c r="U7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.209821428571428</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.032738095238095</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.141534391534391</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>2</v>
+      <c r="AF7" s="2" t="n">
+        <v>12.1</v>
       </c>
     </row>
     <row r="8">
@@ -788,17 +1053,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11.05472932778108</v>
+        <v>4213.832199546485</v>
       </c>
       <c r="D8" t="n">
-        <v>17.52497428510247</v>
+        <v>342.1542598520006</v>
       </c>
       <c r="E8" t="n">
-        <v>14.26690762217452</v>
+        <v>278.5443869091216</v>
       </c>
       <c r="F8" t="n">
         <v>1.228365301662433</v>
@@ -807,24 +1072,54 @@
         <v>0.4523172999675424</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5866996951219512</v>
+        <v>1.783854166666667</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6443407012195123</v>
+        <v>12.57998511904762</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6155201981707317</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>4.476877289377288</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>12.57998511904762</v>
+      </c>
+      <c r="P8" t="n">
+        <v>11.45461309523809</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5.54501488095238</v>
+      </c>
+      <c r="U8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.783854166666667</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.642857142857142</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.861979166666667</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.5842987804878049</v>
+      <c r="AF8" s="2" t="n">
+        <v>1.755301339285714</v>
       </c>
     </row>
     <row r="9">
@@ -835,17 +1130,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11.01487209994051</v>
+        <v>4198.639455782312</v>
       </c>
       <c r="D9" t="n">
-        <v>17.93052105787324</v>
+        <v>350.0720777965727</v>
       </c>
       <c r="E9" t="n">
-        <v>14.33344233326796</v>
+        <v>279.8433979352315</v>
       </c>
       <c r="F9" t="n">
         <v>1.250957072346568</v>
@@ -854,24 +1149,54 @@
         <v>0.4305300822771919</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I9" t="n">
-        <v>0.571360518292683</v>
+        <v>2.001488095238095</v>
       </c>
       <c r="J9" t="n">
-        <v>0.651391006097561</v>
+        <v>12.71763392857143</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6113757621951219</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>5.197947668650793</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>12.71763392857143</v>
+      </c>
+      <c r="P9" t="n">
+        <v>11.15513392857143</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>9.534970238095237</v>
+      </c>
+      <c r="U9" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.001488095238095</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.427083333333333</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.218625992063492</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.6586461509146342</v>
+      <c r="AF9" s="2" t="n">
+        <v>12.85928199404762</v>
       </c>
     </row>
     <row r="10">
@@ -882,17 +1207,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10.91552647233789</v>
+        <v>4160.770975056689</v>
       </c>
       <c r="D10" t="n">
-        <v>18.38138156693156</v>
+        <v>358.8745924972353</v>
       </c>
       <c r="E10" t="n">
-        <v>14.27282573537129</v>
+        <v>278.6599310239156</v>
       </c>
       <c r="F10" t="n">
         <v>1.287858613825736</v>
@@ -901,24 +1226,54 @@
         <v>0.4059740278316833</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5857469512195123</v>
+        <v>1.428571428571428</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6293826219512195</v>
+        <v>12.28794642857143</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6075647865853659</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>5.690780573593073</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5.744047619047619</v>
+      </c>
+      <c r="S10" t="n">
+        <v>12.28794642857143</v>
+      </c>
+      <c r="T10" t="n">
+        <v>9.069568452380953</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.428571428571428</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.135044642857142</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.875124007936508</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.6207483803353659</v>
+      <c r="AF10" s="2" t="n">
+        <v>5.15422818232528</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +1284,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10.8661511005354</v>
+        <v>4141.950113378684</v>
       </c>
       <c r="D11" t="n">
-        <v>18.21136783972019</v>
+        <v>355.5552768707275</v>
       </c>
       <c r="E11" t="n">
-        <v>14.21466045263337</v>
+        <v>277.524323122842</v>
       </c>
       <c r="F11" t="n">
         <v>1.281167981493811</v>
@@ -948,16 +1303,54 @@
         <v>0.4117185844207651</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6051829268292683</v>
+        <v>1.640625</v>
       </c>
       <c r="J11" t="n">
-        <v>0.641577743902439</v>
+        <v>12.52604166666667</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6233803353658537</v>
+        <v>5.536897997835498</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4.92001488095238</v>
+      </c>
+      <c r="S11" t="n">
+        <v>12.52604166666667</v>
+      </c>
+      <c r="T11" t="n">
+        <v>8.816964285714285</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.640625</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.803509424603174</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="12">
@@ -968,35 +1361,73 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.74092801903629</v>
+        <v>4094.217687074829</v>
       </c>
       <c r="D12" t="n">
-        <v>18.74550183226422</v>
+        <v>365.9836072013492</v>
       </c>
       <c r="E12" t="n">
-        <v>14.34181170928769</v>
+        <v>280.006800038474</v>
       </c>
       <c r="F12" t="n">
-        <v>1.307052568548555</v>
+        <v>1.307052568548556</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3841116925533153</v>
+        <v>0.3841116925533152</v>
       </c>
       <c r="H12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.408110119047619</v>
+      </c>
+      <c r="J12" t="n">
+        <v>13.14732142857143</v>
+      </c>
+      <c r="K12" t="n">
+        <v>6.847511574074074</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5.4296875</v>
+      </c>
+      <c r="S12" t="n">
+        <v>13.14732142857143</v>
+      </c>
+      <c r="T12" t="n">
+        <v>9.021267361111111</v>
+      </c>
+      <c r="U12" t="n">
         <v>3</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.5721227134146342</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.6733993902439025</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.6166793699186992</v>
+      <c r="V12" t="n">
+        <v>4.341517857142857</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.750372023809524</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.408110119047619</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="n">
+        <v>14.16905824829932</v>
       </c>
     </row>
     <row r="13">
@@ -1007,35 +1438,73 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10.67400356930399</v>
+        <v>4068.707482993197</v>
       </c>
       <c r="D13" t="n">
-        <v>18.75141990184784</v>
+        <v>366.0991504646483</v>
       </c>
       <c r="E13" t="n">
-        <v>14.32160615921021</v>
+        <v>279.6123107274373</v>
       </c>
       <c r="F13" t="n">
         <v>1.309309842303465</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3814774663133495</v>
+        <v>0.3814774663133494</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5453506097560976</v>
+        <v>1.58110119047619</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6707317073170732</v>
+        <v>13.09523809523809</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5998475609756099</v>
+        <v>6.335379464285714</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>5.171130952380952</v>
+      </c>
+      <c r="S13" t="n">
+        <v>13.09523809523809</v>
+      </c>
+      <c r="T13" t="n">
+        <v>9.063740079365077</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.58110119047619</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.465401785714286</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.242838541666667</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AF13" s="2" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="14">
@@ -1046,35 +1515,73 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10.65734681737061</v>
+        <v>4062.358276643991</v>
       </c>
       <c r="D14" t="n">
-        <v>18.5848729203387</v>
+        <v>362.8475189208984</v>
       </c>
       <c r="E14" t="n">
-        <v>14.1979216337204</v>
+        <v>277.1975176107316</v>
       </c>
       <c r="F14" t="n">
         <v>1.308985455744395</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3877392549301849</v>
+        <v>0.3877392549301848</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5897484756097561</v>
+        <v>1.473214285714286</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6810213414634146</v>
+        <v>13.29613095238095</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6353849085365854</v>
+        <v>5.246930803571428</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>4.756324404761904</v>
+      </c>
+      <c r="S14" t="n">
+        <v>13.29613095238095</v>
+      </c>
+      <c r="T14" t="n">
+        <v>8.201884920634919</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.473214285714286</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.49032738095238</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.291976686507936</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="n">
+        <v>11.81584821428571</v>
       </c>
     </row>
     <row r="15">
@@ -1085,35 +1592,76 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10.61124330755503</v>
+        <v>4044.784580498866</v>
       </c>
       <c r="D15" t="n">
-        <v>18.33505238847035</v>
+        <v>357.9700704415639</v>
       </c>
       <c r="E15" t="n">
-        <v>14.10036062903521</v>
+        <v>275.2927551383063</v>
       </c>
       <c r="F15" t="n">
         <v>1.300325067623813</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3966539891113111</v>
+        <v>0.3966539891113112</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5920350609756098</v>
+        <v>1.393229166666667</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7063643292682927</v>
+        <v>13.79092261904762</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6491996951219512</v>
+        <v>4.813456632653062</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>13.79092261904762</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>11.55877976190476</v>
+      </c>
+      <c r="P15" t="n">
+        <v>6.389508928571428</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6.1328125</v>
+      </c>
+      <c r="U15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.393229166666667</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.45126488095238</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.951636904761904</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="n">
+        <v>8.49609375</v>
       </c>
     </row>
     <row r="16">
@@ -1124,35 +1672,76 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10.54164187983343</v>
+        <v>4018.253968253968</v>
       </c>
       <c r="D16" t="n">
-        <v>18.09605266989731</v>
+        <v>353.3038854598999</v>
       </c>
       <c r="E16" t="n">
-        <v>14.07770370855564</v>
+        <v>274.8504057384673</v>
       </c>
       <c r="F16" t="n">
         <v>1.285440654564959</v>
       </c>
       <c r="G16" t="n">
-        <v>0.404529706197828</v>
+        <v>0.4045297061978278</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5967987804878049</v>
+        <v>1.38764880952381</v>
       </c>
       <c r="J16" t="n">
-        <v>0.715796493902439</v>
+        <v>13.9750744047619</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6562976371951219</v>
+        <v>4.896548763736262</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>13.9750744047619</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>11.65178571428571</v>
+      </c>
+      <c r="P16" t="n">
+        <v>6.850818452380952</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.819568452380953</v>
+      </c>
+      <c r="U16" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.38764880952381</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.547991071428571</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.9286541005291</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="n">
+        <v>6.210751488095238</v>
       </c>
     </row>
     <row r="17">
@@ -1163,17 +1752,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10.45746579417014</v>
+        <v>3986.167800453514</v>
       </c>
       <c r="D17" t="n">
-        <v>17.90338206291199</v>
+        <v>349.5422212282816</v>
       </c>
       <c r="E17" t="n">
-        <v>14.00279966214808</v>
+        <v>273.3879934038434</v>
       </c>
       <c r="F17" t="n">
         <v>1.27855732388344</v>
@@ -1182,16 +1771,57 @@
         <v>0.4099832910042158</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6189024390243902</v>
+        <v>2.129836309523809</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7224657012195123</v>
+        <v>14.10528273809524</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6706840701219512</v>
+        <v>4.985548305860805</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>14.10528273809524</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.944196428571428</v>
+      </c>
+      <c r="S17" t="n">
+        <v>12.08333333333333</v>
+      </c>
+      <c r="T17" t="n">
+        <v>7.422340029761904</v>
+      </c>
+      <c r="U17" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.129836309523809</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.917410714285714</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.627185639880953</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="n">
+        <v>5.216331845238095</v>
       </c>
     </row>
     <row r="18">
@@ -1202,35 +1832,76 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10.3575252825699</v>
+        <v>3948.072562358276</v>
       </c>
       <c r="D18" t="n">
-        <v>17.89154593246739</v>
+        <v>349.3111348719823</v>
       </c>
       <c r="E18" t="n">
-        <v>13.82441651530382</v>
+        <v>269.9052748225984</v>
       </c>
       <c r="F18" t="n">
         <v>1.294198992967349</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4066025805784488</v>
+        <v>0.4066025805784489</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6135670731707318</v>
+        <v>1.990327380952381</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7104611280487805</v>
+        <v>13.87090773809524</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6620141006097562</v>
+        <v>5.084945436507936</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>13.87090773809524</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>11.97916666666667</v>
+      </c>
+      <c r="P18" t="n">
+        <v>7.953869047619047</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.884672619047619</v>
+      </c>
+      <c r="U18" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.990327380952381</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.192708333333333</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.791341145833333</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF18" s="2" t="n">
+        <v>12.37462797619047</v>
       </c>
     </row>
     <row r="19">
@@ -1241,17 +1912,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10.22159428911362</v>
+        <v>3896.25850340136</v>
       </c>
       <c r="D19" t="n">
-        <v>18.53507704851104</v>
+        <v>361.8753138042632</v>
       </c>
       <c r="E19" t="n">
-        <v>13.72093748464817</v>
+        <v>267.884969938369</v>
       </c>
       <c r="F19" t="n">
         <v>1.350860833616451</v>
@@ -1260,16 +1931,57 @@
         <v>0.3738864375946184</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6217606707317074</v>
+        <v>1.919642857142857</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7156059451219512</v>
+        <v>13.97135416666667</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6686833079268293</v>
+        <v>5.391865079365079</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>13.97135416666667</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>12.1391369047619</v>
+      </c>
+      <c r="T19" t="n">
+        <v>7.57626488095238</v>
+      </c>
+      <c r="U19" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.919642857142857</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.345238095238095</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.917995323129252</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AF19" s="2" t="n">
+        <v>8.620421006944444</v>
       </c>
     </row>
     <row r="20">
@@ -1280,17 +1992,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10.00922070196312</v>
+        <v>3815.306122448979</v>
       </c>
       <c r="D20" t="n">
-        <v>19.18452626902883</v>
+        <v>374.555036681039</v>
       </c>
       <c r="E20" t="n">
-        <v>13.68991119396396</v>
+        <v>267.2792185488201</v>
       </c>
       <c r="F20" t="n">
         <v>1.401362360735219</v>
@@ -1299,16 +2011,57 @@
         <v>0.3417495651106492</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6217606707317074</v>
+        <v>1.729910714285714</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7636242378048781</v>
+        <v>14.90885416666667</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6926924542682927</v>
+        <v>5.846354166666665</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>14.90885416666667</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4.66703869047619</v>
+      </c>
+      <c r="S20" t="n">
+        <v>12.1391369047619</v>
+      </c>
+      <c r="T20" t="n">
+        <v>8.538876488095237</v>
+      </c>
+      <c r="U20" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.729910714285714</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.1796875</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.01312712585034</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AF20" s="2" t="n">
+        <v>7.85</v>
       </c>
     </row>
     <row r="21">
@@ -1319,17 +2072,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9.873884592504462</v>
+        <v>3763.718820861678</v>
       </c>
       <c r="D21" t="n">
-        <v>19.02043058232563</v>
+        <v>371.3512637501671</v>
       </c>
       <c r="E21" t="n">
-        <v>13.66378756558023</v>
+        <v>266.7691858041854</v>
       </c>
       <c r="F21" t="n">
         <v>1.392032076833444</v>
@@ -1338,16 +2091,57 @@
         <v>0.3429708599639644</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6326219512195123</v>
+        <v>1.765252976190476</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7458079268292683</v>
+        <v>14.5610119047619</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6892149390243902</v>
+        <v>5.583361950549451</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>14.5610119047619</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>12.35119047619048</v>
+      </c>
+      <c r="P21" t="n">
+        <v>8.7890625</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>8.742559523809524</v>
+      </c>
+      <c r="U21" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.765252976190476</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.428943452380953</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.126653439153439</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF21" s="2" t="n">
+        <v>4.341517857142857</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2151,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AF22" s="2" t="n">
+        <v>1.750372023809524</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2173,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="n">
+        <v>1.408110119047619</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2190,70 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AF24" s="2" t="n">
+        <v>1.773574561403509</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF25" s="2" t="n">
+        <v>4.222372337092732</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AF26" s="2" t="n">
+        <v>2.870331640846796</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AF27" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/37/Filled_2D_sections/sagittal/week37_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/37/Filled_2D_sections/sagittal/week37_sagittal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2259,4 +2465,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week37_sagittal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4066.309523809523</v>
+      </c>
+      <c r="D10" t="n">
+        <v>147.6290948661117</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3763.718820861678</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4272.108843537415</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>353.9828570087751</v>
+      </c>
+      <c r="D11" t="n">
+        <v>14.70510028564644</v>
+      </c>
+      <c r="E11" t="n">
+        <v>321.8554897535415</v>
+      </c>
+      <c r="F11" t="n">
+        <v>380.703459013076</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.281383877412893</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.06503812183538044</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.152227157473596</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.401362360735219</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.4107589504898279</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.04724855842123084</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3354596530008671</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5182392841836267</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis0_s00_idx0186.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis0_s01_idx0188.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>12</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>9</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis0_s02_idx0189.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>13</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>13</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>9</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis0_s03_idx0190.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>13</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>10</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis0_s04_idx0191.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>11</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>11</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis0_s05_idx0192.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>12</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>12</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis0_s06_idx0193.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>13</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>13</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>10</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis0_s07_idx0194.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>12</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>9</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>12</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis0_s08_idx0195.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>11</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>11</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis0_s09_idx0196.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>11</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>11</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis0_s10_idx0198.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>9</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>9</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis0_s11_idx0199.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis0_s12_idx0200.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>12</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>12</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis0_s13_idx0201.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>14</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>10</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>14</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>10</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis0_s14_idx0202.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>13</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>13</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>9</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis0_s15_idx0203.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>13</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>13</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>8</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis0_s16_idx0204.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>12</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>12</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>8</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis0_s17_idx0205.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>12</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>12</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis0_s18_idx0206.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>12</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>12</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis0_s19_idx0207.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>13</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>9</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>13</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>9</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.252366181526625</v>
+      </c>
+      <c r="E40" t="n">
+        <v>9</v>
+      </c>
+      <c r="F40" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.4893604849295929</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.119210247874531</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.084403234046921</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>7</v>
+      </c>
+      <c r="C48" t="n">
+        <v>14.16905824829932</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.4110129563329804</v>
+      </c>
+      <c r="E48" t="n">
+        <v>13.79092261904762</v>
+      </c>
+      <c r="F48" t="n">
+        <v>14.90885416666667</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>78</v>
+      </c>
+      <c r="C49" t="n">
+        <v>8.724411439255189</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.606278973003068</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.66703869047619</v>
+      </c>
+      <c r="F49" t="n">
+        <v>13.29613095238095</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>157</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.890660543676069</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.699366611620419</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.38764880952381</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.642857142857142</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>